--- a/reports/셀린느/history/2026-09-27/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/history/2026-09-27/셀린느_league_mgf_report.xlsx
@@ -194,7 +194,7 @@
     <t>Scania 12</t>
   </si>
   <si>
-    <t>2855</t>
+    <t>2858</t>
   </si>
   <si>
     <t>154위</t>
@@ -962,22 +962,22 @@
     <t>44경 6319조 8919억 3757만</t>
   </si>
   <si>
+    <t>독고사수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
+  </si>
+  <si>
+    <t>11경 8522조 8998억 4569만</t>
+  </si>
+  <si>
     <t>시든꽃에물을</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%A0%EA%BD%83%EC%97%90%EB%AC%BC%EC%9D%84</t>
   </si>
   <si>
-    <t>11경 8161조 4813억 4542만</t>
-  </si>
-  <si>
-    <t>독고사수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
-  </si>
-  <si>
-    <t>11경 5422조 1567억 4724만</t>
+    <t>11경 8194조 6927억 6358만</t>
   </si>
   <si>
     <t>딩느</t>
@@ -1010,6 +1010,15 @@
     <t>2경 5047조 6740억 1185만</t>
   </si>
   <si>
+    <t>가푸츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1경 9281조 1467억 3386만</t>
+  </si>
+  <si>
     <t>동작대교</t>
   </si>
   <si>
@@ -1019,22 +1028,13 @@
     <t>1경 8332조 1425억 2718만</t>
   </si>
   <si>
-    <t>가푸츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1경 8056조 278억 5726만</t>
-  </si>
-  <si>
     <t>나야츄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 2057조 2363억 8618만</t>
+    <t>1경 4393조 6778억 3625만</t>
   </si>
   <si>
     <t>날아라순자</t>
@@ -1064,46 +1064,55 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%8D%95%ED%96%89</t>
   </si>
   <si>
+    <t>7189조 6952억 919만</t>
+  </si>
+  <si>
+    <t>유졍츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
+  </si>
+  <si>
+    <t>6051조 1417억 7599만</t>
+  </si>
+  <si>
+    <t>lNOVAl</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=lNOVAl</t>
+  </si>
+  <si>
+    <t>5566조 6120억 2581만</t>
+  </si>
+  <si>
+    <t>천상츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
+  </si>
+  <si>
+    <t>5471조 457억 5918만</t>
+  </si>
+  <si>
+    <t>넹또</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%B9%EB%98%90</t>
+  </si>
+  <si>
+    <t>5235조 7337억 1600만</t>
+  </si>
+  <si>
+    <t>직만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%A7%8C</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>7189조 6952억 919만</t>
-  </si>
-  <si>
-    <t>유졍츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
-  </si>
-  <si>
-    <t>6051조 1417억 7599만</t>
-  </si>
-  <si>
-    <t>lNOVAl</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=lNOVAl</t>
-  </si>
-  <si>
-    <t>5566조 6120억 2581만</t>
-  </si>
-  <si>
-    <t>천상츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
-  </si>
-  <si>
-    <t>5471조 457억 5918만</t>
-  </si>
-  <si>
-    <t>넹또</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%B9%EB%98%90</t>
-  </si>
-  <si>
-    <t>5235조 7337억 1600만</t>
+    <t>4964조 8365억 8281만</t>
   </si>
   <si>
     <t>딤츄</t>
@@ -1115,15 +1124,6 @@
     <t>4871조 996억 906만</t>
   </si>
   <si>
-    <t>직만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>4841조 9029억 1724만</t>
-  </si>
-  <si>
     <t>Dollmeng2</t>
   </si>
   <si>
@@ -1133,22 +1133,22 @@
     <t>4171조 7934억 1773만</t>
   </si>
   <si>
+    <t>파숙츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
+  </si>
+  <si>
+    <t>3453조 2261억 2721만</t>
+  </si>
+  <si>
     <t>조림츄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>3414조 1764억 9443만</t>
-  </si>
-  <si>
-    <t>파숙츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
-  </si>
-  <si>
-    <t>3357조 9102억 6954만</t>
+    <t>3438조 7426억 835만</t>
   </si>
   <si>
     <t>나야김대장</t>
@@ -1157,7 +1157,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
   </si>
   <si>
-    <t>3323조 2601억 4498만</t>
+    <t>3387조 2396억 6749만</t>
   </si>
   <si>
     <t>화정츄</t>
@@ -1196,7 +1196,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B6%81%EA%B8%88%EC%A6%9D%EC%9C%A0%EB%B0%9C</t>
   </si>
   <si>
-    <t>2364조 6292억 9802만</t>
+    <t>2644조 2846억 1124만</t>
   </si>
   <si>
     <t>현유수</t>
@@ -4648,10 +4648,10 @@
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>313</v>
@@ -4680,10 +4680,10 @@
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>316</v>
@@ -4808,7 +4808,7 @@
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>180</v>
@@ -4840,7 +4840,7 @@
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>180</v>
@@ -4971,10 +4971,10 @@
         <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4988,13 +4988,13 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
@@ -5003,10 +5003,10 @@
         <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5020,13 +5020,13 @@
         <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
@@ -5038,7 +5038,7 @@
         <v>325</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5052,13 +5052,13 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
@@ -5070,7 +5070,7 @@
         <v>338</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5084,13 +5084,13 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
@@ -5102,7 +5102,7 @@
         <v>325</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5116,22 +5116,22 @@
         <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>361</v>
@@ -5160,10 +5160,10 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>364</v>
@@ -5195,7 +5195,7 @@
         <v>260</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>367</v>
@@ -5227,7 +5227,7 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>345</v>
+        <v>298</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>370</v>
@@ -5259,7 +5259,7 @@
         <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>298</v>
+        <v>360</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>373</v>
@@ -5291,7 +5291,7 @@
         <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>376</v>
@@ -5419,7 +5419,7 @@
         <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>389</v>
@@ -5451,7 +5451,7 @@
         <v>197</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>392</v>
